--- a/Optimal.entrap/Data/20260629_optimalentrapment_experiment_data_github.xlsx
+++ b/Optimal.entrap/Data/20260629_optimalentrapment_experiment_data_github.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joyobrien/GitHub/VirosporeQuant/Optimal.entrap/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2852173C-A9D9-BC49-ADA8-C33F218D4407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F879876-653A-3E48-927C-9717907AFBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-260" yWindow="680" windowWidth="30240" windowHeight="17880" xr2:uid="{55AD2BB1-5889-614B-96D7-3681C427E69F}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17880" xr2:uid="{55AD2BB1-5889-614B-96D7-3681C427E69F}"/>
   </bookViews>
   <sheets>
     <sheet name="opt.e" sheetId="4" r:id="rId1"/>
@@ -477,14 +477,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5215,7 +5214,7 @@
       <c r="J92" s="1">
         <v>1E-3</v>
       </c>
-      <c r="K92" s="6">
+      <c r="K92">
         <v>6</v>
       </c>
       <c r="L92" s="1">
@@ -5263,7 +5262,7 @@
       <c r="J93" s="1">
         <v>1E-4</v>
       </c>
-      <c r="K93" s="6">
+      <c r="K93">
         <v>12</v>
       </c>
       <c r="L93" s="1">
@@ -5311,7 +5310,7 @@
       <c r="J94" s="1">
         <v>1E-4</v>
       </c>
-      <c r="K94" s="6">
+      <c r="K94">
         <v>58</v>
       </c>
       <c r="L94" s="1">
@@ -5359,7 +5358,7 @@
       <c r="J95" s="1">
         <v>1E-4</v>
       </c>
-      <c r="K95" s="6">
+      <c r="K95">
         <v>136</v>
       </c>
       <c r="L95" s="1">
@@ -5407,7 +5406,7 @@
       <c r="J96" s="1">
         <v>0.01</v>
       </c>
-      <c r="K96" s="6">
+      <c r="K96">
         <v>31</v>
       </c>
       <c r="L96" s="1">
@@ -5455,7 +5454,7 @@
       <c r="J97" s="1">
         <v>1E-3</v>
       </c>
-      <c r="K97" s="6">
+      <c r="K97">
         <v>72</v>
       </c>
       <c r="L97" s="1">
@@ -5503,7 +5502,7 @@
       <c r="J98" s="1">
         <v>0.01</v>
       </c>
-      <c r="K98" s="6">
+      <c r="K98">
         <v>152</v>
       </c>
       <c r="L98" s="1">
@@ -5551,7 +5550,7 @@
       <c r="J99" s="1">
         <v>0.01</v>
       </c>
-      <c r="K99" s="6">
+      <c r="K99">
         <v>155</v>
       </c>
       <c r="L99" s="1">
@@ -5599,7 +5598,7 @@
       <c r="J100" s="1">
         <v>0.01</v>
       </c>
-      <c r="K100" s="6">
+      <c r="K100">
         <v>226</v>
       </c>
       <c r="L100" s="1">
@@ -5647,7 +5646,7 @@
       <c r="J101" s="1">
         <v>1E-4</v>
       </c>
-      <c r="K101" s="6">
+      <c r="K101">
         <v>585</v>
       </c>
       <c r="L101" s="1">
@@ -5695,7 +5694,7 @@
       <c r="J102" s="1">
         <v>1E-4</v>
       </c>
-      <c r="K102" s="6">
+      <c r="K102">
         <v>301</v>
       </c>
       <c r="L102" s="1">
@@ -5743,9 +5742,17 @@
       <c r="J103" s="1">
         <v>1E-3</v>
       </c>
-      <c r="K103" s="6"/>
-      <c r="L103" s="1"/>
-      <c r="M103" s="1"/>
+      <c r="K103" s="1">
+        <v>799</v>
+      </c>
+      <c r="L103" s="1">
+        <f t="shared" si="4"/>
+        <v>7990000</v>
+      </c>
+      <c r="M103" s="1">
+        <f t="shared" si="5"/>
+        <v>1141428.5714285714</v>
+      </c>
       <c r="N103" s="1">
         <f t="shared" si="6"/>
         <v>75714285.714285716</v>
@@ -5783,7 +5790,7 @@
       <c r="J104" s="1">
         <v>0.01</v>
       </c>
-      <c r="K104" s="6">
+      <c r="K104">
         <v>192</v>
       </c>
       <c r="L104" s="1">
@@ -5831,7 +5838,7 @@
       <c r="J105" s="1">
         <v>0.01</v>
       </c>
-      <c r="K105" s="6">
+      <c r="K105">
         <v>213</v>
       </c>
       <c r="L105" s="1">
@@ -5879,7 +5886,7 @@
       <c r="J106" s="1">
         <v>0.01</v>
       </c>
-      <c r="K106" s="6">
+      <c r="K106">
         <v>345</v>
       </c>
       <c r="L106" s="1">
@@ -5927,7 +5934,7 @@
       <c r="J107" s="1">
         <v>0.01</v>
       </c>
-      <c r="K107" s="6">
+      <c r="K107">
         <v>254</v>
       </c>
       <c r="L107" s="1">
@@ -5975,7 +5982,7 @@
       <c r="J108" s="1">
         <v>1E-3</v>
       </c>
-      <c r="K108" s="6">
+      <c r="K108">
         <v>181</v>
       </c>
       <c r="L108" s="1">
@@ -6023,7 +6030,7 @@
       <c r="J109" s="1">
         <v>0.01</v>
       </c>
-      <c r="K109" s="6">
+      <c r="K109">
         <v>288</v>
       </c>
       <c r="L109" s="1">
@@ -6071,7 +6078,7 @@
       <c r="J110" s="1">
         <v>1E-3</v>
       </c>
-      <c r="K110" s="6">
+      <c r="K110">
         <v>579</v>
       </c>
       <c r="L110" s="1">
@@ -6119,7 +6126,7 @@
       <c r="J111" s="1">
         <v>1E-3</v>
       </c>
-      <c r="K111" s="6">
+      <c r="K111">
         <v>71</v>
       </c>
       <c r="L111" s="1">
@@ -6167,7 +6174,7 @@
       <c r="J112" s="1">
         <v>1E-4</v>
       </c>
-      <c r="K112" s="6">
+      <c r="K112">
         <v>275</v>
       </c>
       <c r="L112" s="1">
@@ -6215,7 +6222,7 @@
       <c r="J113" s="1">
         <v>0.01</v>
       </c>
-      <c r="K113" s="6">
+      <c r="K113">
         <v>182</v>
       </c>
       <c r="L113" s="1">
@@ -6263,7 +6270,7 @@
       <c r="J114" s="1">
         <v>1E-3</v>
       </c>
-      <c r="K114" s="6">
+      <c r="K114">
         <v>299</v>
       </c>
       <c r="L114" s="1">
@@ -6311,7 +6318,7 @@
       <c r="J115" s="1">
         <v>0.01</v>
       </c>
-      <c r="K115" s="6">
+      <c r="K115">
         <v>172</v>
       </c>
       <c r="L115" s="1">
@@ -6359,7 +6366,7 @@
       <c r="J116" s="1">
         <v>0.01</v>
       </c>
-      <c r="K116" s="6">
+      <c r="K116">
         <v>225</v>
       </c>
       <c r="L116" s="1">
@@ -6407,7 +6414,7 @@
       <c r="J117" s="1">
         <v>1E-3</v>
       </c>
-      <c r="K117" s="6">
+      <c r="K117">
         <v>96</v>
       </c>
       <c r="L117" s="1">
@@ -6487,6 +6494,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F7ECD2AE6C84B440A24D77076F6B7AB9" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b3370645adbffe904c26b1373f553030">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f0f9615f-c5bb-4d0d-9154-15db78a898aa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bab3bc09f4ec31363faa9218cb81bc08" ns2:_="">
     <xsd:import namespace="f0f9615f-c5bb-4d0d-9154-15db78a898aa"/>
@@ -6670,15 +6686,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAA2E974-E37A-47AC-AEE9-EC69A7E7453B}">
   <ds:schemaRefs>
@@ -6696,6 +6703,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CD3180F-8EE5-46C7-882B-48471A3D70E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0054097-5515-4A96-BADD-9AC9FC8054C4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6711,12 +6726,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CD3180F-8EE5-46C7-882B-48471A3D70E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>